--- a/output/stock_deviation_2026-03-15.xlsx
+++ b/output/stock_deviation_2026-03-15.xlsx
@@ -740,7 +740,7 @@
         <v>9.6</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>816.578</v>
+        <v>816.574</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>6514</v>
@@ -29197,7 +29197,7 @@
         <v>9.6</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>816.578</v>
+        <v>816.574</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>6514</v>
@@ -58035,7 +58035,7 @@
         <v>9.6</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>816.578</v>
+        <v>816.574</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>6514</v>

--- a/output/stock_deviation_2026-03-15.xlsx
+++ b/output/stock_deviation_2026-03-15.xlsx
@@ -740,7 +740,7 @@
         <v>9.6</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>816.574</v>
+        <v>816.576</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>6514</v>
@@ -4401,7 +4401,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -4415,53 +4415,53 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>生活必需品</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>配当貴族</t>
+          <t>Dow30</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>274.18</v>
+        <v>150.65</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>295.53</v>
+        <v>158.89</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-7.225</v>
+        <v>-5.186</v>
       </c>
       <c r="L57" s="20" t="n">
         <v>1.19</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>1.21</v>
+        <v>2.7</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>1.23</v>
+        <v>2.73</v>
       </c>
       <c r="O57" s="16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="Q57" s="8" t="n">
-        <v>4.421</v>
+        <v>3.406</v>
       </c>
       <c r="R57" s="9" t="n">
-        <v>13354</v>
+        <v>16133</v>
       </c>
     </row>
     <row r="58">
@@ -4469,7 +4469,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -4483,53 +4483,53 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>生活必需品</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Dow30</t>
+          <t>配当貴族</t>
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>150.65</v>
+        <v>274.18</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>158.89</v>
+        <v>295.53</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-5.186</v>
+        <v>-7.225</v>
       </c>
       <c r="L58" s="20" t="n">
         <v>1.19</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>2.7</v>
+        <v>1.21</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>2.73</v>
+        <v>1.23</v>
       </c>
       <c r="O58" s="16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P58" s="7" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="Q58" s="8" t="n">
-        <v>3.407</v>
+        <v>4.421</v>
       </c>
       <c r="R58" s="9" t="n">
-        <v>16133</v>
+        <v>13354</v>
       </c>
     </row>
     <row r="59">
@@ -5081,7 +5081,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -5095,53 +5095,53 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>4151.T</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>協和キリン</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>ヘルスケア</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>配当貴族</t>
+          <t>Nikkei225</t>
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>169.39</v>
+        <v>2331</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>182.94</v>
+        <v>2531.08</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-7.408</v>
+        <v>-7.905</v>
       </c>
       <c r="L67" s="20" t="n">
         <v>1.75</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>1.84</v>
+        <v>2.66</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="O67" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="P67" s="7" t="n">
-        <v>15.3</v>
+        <v>2.71</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P67" s="17" t="n">
+        <v>39.2</v>
       </c>
       <c r="Q67" s="8" t="n">
-        <v>4.86</v>
+        <v>4.886</v>
       </c>
       <c r="R67" s="9" t="n">
-        <v>7121</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="68">
@@ -5149,7 +5149,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -5163,53 +5163,53 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>4151.T</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>協和キリン</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ヘルスケア</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Nikkei225</t>
+          <t>配当貴族</t>
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>2331</v>
+        <v>169.39</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>2531.08</v>
+        <v>182.94</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-7.905</v>
+        <v>-7.408</v>
       </c>
       <c r="L68" s="20" t="n">
         <v>1.75</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>2.66</v>
+        <v>1.84</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="O68" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="P68" s="17" t="n">
-        <v>39.2</v>
+        <v>1.87</v>
+      </c>
+      <c r="O68" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="P68" s="7" t="n">
+        <v>15.3</v>
       </c>
       <c r="Q68" s="8" t="n">
-        <v>4.886</v>
+        <v>4.86</v>
       </c>
       <c r="R68" s="9" t="n">
-        <v>6514</v>
+        <v>7121</v>
       </c>
     </row>
     <row r="69">
@@ -5418,8 +5418,8 @@
       <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="14" t="n">
-        <v>50</v>
+      <c r="B72" s="2" t="n">
+        <v>35</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -5433,17 +5433,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>9007.T</t>
+          <t>6473.T</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>小田急電鉄</t>
+          <t>ジェイテクト</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5452,31 +5452,31 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>1631.5</v>
+        <v>1750</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>1720.3</v>
+        <v>1967.52</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-5.162</v>
+        <v>-11.056</v>
       </c>
       <c r="L72" s="20" t="n">
         <v>2.2</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>2.51</v>
+        <v>2.92</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
-      </c>
-      <c r="P72" s="17" t="n">
-        <v>49.2</v>
+        <v>4</v>
+      </c>
+      <c r="P72" s="7" t="n">
+        <v>18.6</v>
       </c>
       <c r="Q72" s="8" t="n">
-        <v>3.732</v>
+        <v>6.658</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>6514</v>
@@ -5486,8 +5486,8 @@
       <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="n">
-        <v>35</v>
+      <c r="B73" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -5501,17 +5501,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6473.T</t>
+          <t>9007.T</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ジェイテクト</t>
+          <t>小田急電鉄</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5520,31 +5520,31 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>1750</v>
+        <v>1631.5</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1967.52</v>
+        <v>1720.3</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-11.056</v>
+        <v>-5.162</v>
       </c>
       <c r="L73" s="20" t="n">
         <v>2.2</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="O73" t="n">
-        <v>4</v>
-      </c>
-      <c r="P73" s="7" t="n">
-        <v>18.6</v>
+        <v>3</v>
+      </c>
+      <c r="P73" s="17" t="n">
+        <v>49.2</v>
       </c>
       <c r="Q73" s="8" t="n">
-        <v>6.658</v>
+        <v>3.732</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>6514</v>
@@ -6369,7 +6369,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -6383,17 +6383,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>8267.T</t>
+          <t>1332.T</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>イオン</t>
+          <t>日本水産</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>生活必需品</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6402,31 +6402,31 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>2019</v>
+        <v>1354</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>2185.33</v>
+        <v>1467.9</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-7.611</v>
+        <v>-7.759</v>
       </c>
       <c r="L86" s="20" t="n">
         <v>2.85</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0.66</v>
+        <v>2.07</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="O86" t="n">
-        <v>2</v>
+        <v>2.13</v>
+      </c>
+      <c r="O86" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="P86" s="7" t="n">
-        <v>29.6</v>
+        <v>13.2</v>
       </c>
       <c r="Q86" s="8" t="n">
-        <v>5.332</v>
+        <v>5.433</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>6514</v>
@@ -6437,7 +6437,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -6451,17 +6451,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1332.T</t>
+          <t>8267.T</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>日本水産</t>
+          <t>イオン</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>生活必需品</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6470,31 +6470,31 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>1354</v>
+        <v>2019</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>1467.9</v>
+        <v>2185.33</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-7.759</v>
+        <v>-7.611</v>
       </c>
       <c r="L87" s="20" t="n">
         <v>2.85</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>2.07</v>
+        <v>0.66</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="O87" s="2" t="n">
-        <v>6</v>
+        <v>0.68</v>
+      </c>
+      <c r="O87" t="n">
+        <v>2</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>13.2</v>
+        <v>29.6</v>
       </c>
       <c r="Q87" s="8" t="n">
-        <v>5.433</v>
+        <v>5.332</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>6514</v>
@@ -7795,17 +7795,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2502.T</t>
+          <t>5201.T</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>アサヒGHD</t>
+          <t>AGC</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>生活必需品</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7814,31 +7814,29 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>1600</v>
+        <v>5830</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>1672.24</v>
+        <v>6292.48</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>-4.32</v>
+        <v>-7.35</v>
       </c>
       <c r="L107" s="5" t="n">
         <v>3.87</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="N107" s="5" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="O107" s="16" t="n">
-        <v>23</v>
-      </c>
+        <v>3.74</v>
+      </c>
+      <c r="O107" t="inlineStr"/>
       <c r="P107" s="7" t="n">
-        <v>18.8</v>
+        <v>15.9</v>
       </c>
       <c r="Q107" s="8" t="n">
-        <v>4.145</v>
+        <v>5.534</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>6514</v>
@@ -7863,17 +7861,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>5201.T</t>
+          <t>2502.T</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>AGC</t>
+          <t>アサヒGHD</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>生活必需品</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7882,29 +7880,31 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>5830</v>
+        <v>1600</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>6292.48</v>
+        <v>1672.24</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>-7.35</v>
+        <v>-4.32</v>
       </c>
       <c r="L108" s="5" t="n">
         <v>3.87</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="N108" s="5" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="O108" t="inlineStr"/>
+        <v>3.18</v>
+      </c>
+      <c r="O108" s="16" t="n">
+        <v>23</v>
+      </c>
       <c r="P108" s="7" t="n">
-        <v>15.9</v>
+        <v>18.8</v>
       </c>
       <c r="Q108" s="8" t="n">
-        <v>5.534</v>
+        <v>4.145</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>6514</v>
@@ -9075,17 +9075,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>6471.T</t>
+          <t>2501.T</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>日本精工</t>
+          <t>サッポロHD</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>生活必需品</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9094,31 +9094,31 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>1169.5</v>
+        <v>1612</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>1279.48</v>
+        <v>1720.88</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>-8.596</v>
+        <v>-6.327</v>
       </c>
       <c r="L126" s="5" t="n">
         <v>4.68</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>2.91</v>
+        <v>1.12</v>
       </c>
       <c r="N126" s="5" t="n">
-        <v>3.04</v>
+        <v>1.17</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P126" s="7" t="n">
-        <v>20.3</v>
+        <v>14.3</v>
       </c>
       <c r="Q126" s="8" t="n">
-        <v>6.493</v>
+        <v>5.475</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>6514</v>
@@ -9143,17 +9143,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2501.T</t>
+          <t>6471.T</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>サッポロHD</t>
+          <t>日本精工</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>生活必需品</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9162,31 +9162,31 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>1612</v>
+        <v>1169.5</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>1720.88</v>
+        <v>1279.48</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>-6.327</v>
+        <v>-8.596</v>
       </c>
       <c r="L127" s="5" t="n">
         <v>4.68</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>1.12</v>
+        <v>2.91</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>1.17</v>
+        <v>3.04</v>
       </c>
       <c r="O127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P127" s="7" t="n">
-        <v>14.3</v>
+        <v>20.3</v>
       </c>
       <c r="Q127" s="8" t="n">
-        <v>5.475</v>
+        <v>6.493</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>6514</v>
@@ -10695,17 +10695,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>3861.T</t>
+          <t>9020.T</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>王子HD</t>
+          <t>東日本旅客鉄道</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10714,31 +10714,31 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>908.2</v>
+        <v>3721</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>952.6799999999999</v>
+        <v>3810.16</v>
       </c>
       <c r="K150" s="5" t="n">
-        <v>-4.669</v>
+        <v>-2.34</v>
       </c>
       <c r="L150" s="5" t="n">
         <v>5.35</v>
       </c>
       <c r="M150" s="5" t="n">
-        <v>2.64</v>
+        <v>1.61</v>
       </c>
       <c r="N150" s="5" t="n">
-        <v>2.78</v>
+        <v>1.7</v>
       </c>
       <c r="O150" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P150" s="7" t="n">
-        <v>8.1</v>
+        <v>11.4</v>
       </c>
       <c r="Q150" s="8" t="n">
-        <v>4.871</v>
+        <v>3.773</v>
       </c>
       <c r="R150" s="9" t="n">
         <v>6514</v>
@@ -10763,17 +10763,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>9020.T</t>
+          <t>3861.T</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>東日本旅客鉄道</t>
+          <t>王子HD</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -10782,31 +10782,31 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>3721</v>
+        <v>908.2</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>3810.16</v>
+        <v>952.6799999999999</v>
       </c>
       <c r="K151" s="5" t="n">
-        <v>-2.34</v>
+        <v>-4.669</v>
       </c>
       <c r="L151" s="5" t="n">
         <v>5.35</v>
       </c>
       <c r="M151" s="5" t="n">
-        <v>1.61</v>
+        <v>2.64</v>
       </c>
       <c r="N151" s="5" t="n">
-        <v>1.7</v>
+        <v>2.78</v>
       </c>
       <c r="O151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P151" s="7" t="n">
-        <v>11.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q151" s="8" t="n">
-        <v>3.773</v>
+        <v>4.871</v>
       </c>
       <c r="R151" s="9" t="n">
         <v>6514</v>
@@ -10817,7 +10817,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -10831,17 +10831,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>7752.T</t>
+          <t>5301.T</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>リコー</t>
+          <t>東海カーボン</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10850,34 +10850,32 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>1347.5</v>
+        <v>959.7</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>1434.8</v>
+        <v>1046.57</v>
       </c>
       <c r="K152" s="5" t="n">
-        <v>-6.084</v>
+        <v>-8.301</v>
       </c>
       <c r="L152" s="5" t="n">
         <v>5.41</v>
       </c>
       <c r="M152" s="5" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="N152" s="5" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="O152" t="n">
-        <v>4</v>
-      </c>
-      <c r="P152" s="7" t="n">
-        <v>24.8</v>
+        <v>3.3</v>
+      </c>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" s="17" t="n">
+        <v>48.3</v>
       </c>
       <c r="Q152" s="8" t="n">
-        <v>5.541</v>
+        <v>6.765</v>
       </c>
       <c r="R152" s="9" t="n">
-        <v>6687</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="153">
@@ -10885,7 +10883,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -10899,17 +10897,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>5301.T</t>
+          <t>7752.T</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>東海カーボン</t>
+          <t>リコー</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10918,32 +10916,34 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>959.7</v>
+        <v>1347.5</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>1046.57</v>
+        <v>1434.8</v>
       </c>
       <c r="K153" s="5" t="n">
-        <v>-8.301</v>
+        <v>-6.084</v>
       </c>
       <c r="L153" s="5" t="n">
         <v>5.41</v>
       </c>
       <c r="M153" s="5" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="N153" s="5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" s="17" t="n">
-        <v>48.3</v>
+        <v>2.97</v>
+      </c>
+      <c r="O153" t="n">
+        <v>4</v>
+      </c>
+      <c r="P153" s="7" t="n">
+        <v>24.8</v>
       </c>
       <c r="Q153" s="8" t="n">
-        <v>6.765</v>
+        <v>5.541</v>
       </c>
       <c r="R153" s="9" t="n">
-        <v>6514</v>
+        <v>6687</v>
       </c>
     </row>
     <row r="154">
@@ -12300,8 +12300,8 @@
       <c r="A174" t="n">
         <v>173</v>
       </c>
-      <c r="B174" s="2" t="n">
-        <v>32</v>
+      <c r="B174" t="n">
+        <v>20</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -12315,61 +12315,61 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>DIS</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>不動産</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>配当貴族</t>
+          <t>Dow30</t>
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>64.44</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>65.25</v>
+        <v>104.41</v>
       </c>
       <c r="K174" s="5" t="n">
-        <v>-1.248</v>
+        <v>-4.901</v>
       </c>
       <c r="L174" s="5" t="n">
         <v>6.15</v>
       </c>
       <c r="M174" s="5" t="n">
-        <v>5.43</v>
+        <v>1.01</v>
       </c>
       <c r="N174" s="5" t="n">
-        <v>5.77</v>
+        <v>1.07</v>
       </c>
       <c r="O174" t="n">
-        <v>1</v>
-      </c>
-      <c r="P174" s="7" t="n">
-        <v>4.6</v>
+        <v>2</v>
+      </c>
+      <c r="P174" s="17" t="n">
+        <v>49.7</v>
       </c>
       <c r="Q174" s="8" t="n">
-        <v>3.809</v>
+        <v>5.521</v>
       </c>
       <c r="R174" s="9" t="n">
-        <v>7879</v>
+        <v>16133</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
         <v>174</v>
       </c>
-      <c r="B175" t="n">
-        <v>20</v>
+      <c r="B175" s="2" t="n">
+        <v>32</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -12383,53 +12383,53 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>DIS</t>
+          <t>O</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Disney</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>不動産</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Dow30</t>
+          <t>配当貴族</t>
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>99.29000000000001</v>
+        <v>64.44</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>104.41</v>
+        <v>65.25</v>
       </c>
       <c r="K175" s="5" t="n">
-        <v>-4.901</v>
+        <v>-1.248</v>
       </c>
       <c r="L175" s="5" t="n">
         <v>6.15</v>
       </c>
       <c r="M175" s="5" t="n">
-        <v>1.01</v>
+        <v>5.43</v>
       </c>
       <c r="N175" s="5" t="n">
-        <v>1.07</v>
+        <v>5.77</v>
       </c>
       <c r="O175" t="n">
-        <v>2</v>
-      </c>
-      <c r="P175" s="17" t="n">
-        <v>49.7</v>
+        <v>1</v>
+      </c>
+      <c r="P175" s="7" t="n">
+        <v>4.6</v>
       </c>
       <c r="Q175" s="8" t="n">
-        <v>5.521</v>
+        <v>3.809</v>
       </c>
       <c r="R175" s="9" t="n">
-        <v>16133</v>
+        <v>7879</v>
       </c>
     </row>
     <row r="176">
@@ -13597,17 +13597,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>3659.T</t>
+          <t>3088.T</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>マツキヨココカラ</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>ヘルスケア</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -13616,34 +13616,34 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>3012</v>
+        <v>2463</v>
       </c>
       <c r="J193" s="4" t="n">
-        <v>3242.76</v>
+        <v>2552.58</v>
       </c>
       <c r="K193" s="5" t="n">
-        <v>-7.116</v>
+        <v>-3.509</v>
       </c>
       <c r="L193" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="M193" s="5" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="N193" s="5" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="O193" t="n">
-        <v>2</v>
-      </c>
-      <c r="P193" s="17" t="n">
-        <v>31.9</v>
+        <v>4</v>
+      </c>
+      <c r="P193" s="7" t="n">
+        <v>26.7</v>
       </c>
       <c r="Q193" s="8" t="n">
-        <v>6.906</v>
+        <v>5.143</v>
       </c>
       <c r="R193" s="9" t="n">
-        <v>3481</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="194">
@@ -13665,17 +13665,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>3088.T</t>
+          <t>3659.T</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>マツキヨココカラ</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>ヘルスケア</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13684,34 +13684,34 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>2463</v>
+        <v>3012</v>
       </c>
       <c r="J194" s="4" t="n">
-        <v>2552.58</v>
+        <v>3242.76</v>
       </c>
       <c r="K194" s="5" t="n">
-        <v>-3.509</v>
+        <v>-7.116</v>
       </c>
       <c r="L194" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="M194" s="5" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="N194" s="5" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="O194" t="n">
-        <v>4</v>
-      </c>
-      <c r="P194" s="7" t="n">
-        <v>26.7</v>
+        <v>2</v>
+      </c>
+      <c r="P194" s="17" t="n">
+        <v>31.9</v>
       </c>
       <c r="Q194" s="8" t="n">
-        <v>5.143</v>
+        <v>6.906</v>
       </c>
       <c r="R194" s="9" t="n">
-        <v>6252</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="195">
@@ -14207,53 +14207,53 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>6305.T</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>日立建機</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>配当貴族</t>
+          <t>Nikkei225</t>
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>108.71</v>
+        <v>5918</v>
       </c>
       <c r="J202" s="4" t="n">
-        <v>112.71</v>
+        <v>6374.04</v>
       </c>
       <c r="K202" s="5" t="n">
-        <v>-3.548</v>
+        <v>-7.155</v>
       </c>
       <c r="L202" s="5" t="n">
         <v>7.06</v>
       </c>
       <c r="M202" s="5" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="N202" s="5" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="O202" s="16" t="n">
-        <v>41</v>
+        <v>3.17</v>
+      </c>
+      <c r="O202" t="n">
+        <v>1</v>
       </c>
       <c r="P202" s="7" t="n">
-        <v>7</v>
+        <v>15.8</v>
       </c>
       <c r="Q202" s="8" t="n">
-        <v>5.388</v>
+        <v>7.006</v>
       </c>
       <c r="R202" s="9" t="n">
-        <v>11568</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="203">
@@ -14261,7 +14261,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -14275,53 +14275,53 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>NASDAQ100</t>
+          <t>配当貴族</t>
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>613.71</v>
+        <v>108.71</v>
       </c>
       <c r="J203" s="4" t="n">
-        <v>651.04</v>
+        <v>112.71</v>
       </c>
       <c r="K203" s="5" t="n">
-        <v>-5.734</v>
+        <v>-3.548</v>
       </c>
       <c r="L203" s="5" t="n">
         <v>7.06</v>
       </c>
       <c r="M203" s="5" t="n">
-        <v>0.34</v>
+        <v>2.7</v>
       </c>
       <c r="N203" s="5" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="O203" t="n">
-        <v>1</v>
+        <v>2.89</v>
+      </c>
+      <c r="O203" s="16" t="n">
+        <v>41</v>
       </c>
       <c r="P203" s="7" t="n">
-        <v>22.2</v>
+        <v>7</v>
       </c>
       <c r="Q203" s="8" t="n">
-        <v>6.57</v>
+        <v>5.388</v>
       </c>
       <c r="R203" s="9" t="n">
-        <v>3450</v>
+        <v>11568</v>
       </c>
     </row>
     <row r="204">
@@ -14329,7 +14329,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -14343,53 +14343,53 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>6305.T</t>
+          <t>META</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>日立建機</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Nikkei225</t>
+          <t>NASDAQ100</t>
         </is>
       </c>
       <c r="I204" s="4" t="n">
-        <v>5918</v>
+        <v>613.71</v>
       </c>
       <c r="J204" s="4" t="n">
-        <v>6374.04</v>
+        <v>651.04</v>
       </c>
       <c r="K204" s="5" t="n">
-        <v>-7.155</v>
+        <v>-5.734</v>
       </c>
       <c r="L204" s="5" t="n">
         <v>7.06</v>
       </c>
       <c r="M204" s="5" t="n">
-        <v>2.96</v>
+        <v>0.34</v>
       </c>
       <c r="N204" s="5" t="n">
-        <v>3.17</v>
+        <v>0.37</v>
       </c>
       <c r="O204" t="n">
         <v>1</v>
       </c>
       <c r="P204" s="7" t="n">
-        <v>15.8</v>
+        <v>22.2</v>
       </c>
       <c r="Q204" s="8" t="n">
-        <v>7.006</v>
+        <v>6.57</v>
       </c>
       <c r="R204" s="9" t="n">
-        <v>6255</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="205">
@@ -14865,7 +14865,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -14879,17 +14879,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>8750.T</t>
+          <t>9531.T</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>第一生命HD</t>
+          <t>東京ガス</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>公益</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -14898,32 +14898,34 @@
         </is>
       </c>
       <c r="I212" s="4" t="n">
-        <v>1421</v>
+        <v>7584</v>
       </c>
       <c r="J212" s="4" t="n">
-        <v>1502.86</v>
+        <v>7609.92</v>
       </c>
       <c r="K212" s="5" t="n">
-        <v>-5.447</v>
+        <v>-0.341</v>
       </c>
       <c r="L212" s="5" t="n">
         <v>7.45</v>
       </c>
       <c r="M212" s="5" t="n">
-        <v>2.41</v>
+        <v>1.05</v>
       </c>
       <c r="N212" s="5" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O212" t="inlineStr"/>
+        <v>1.13</v>
+      </c>
+      <c r="O212" t="n">
+        <v>2</v>
+      </c>
       <c r="P212" s="7" t="n">
-        <v>11.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q212" s="8" t="n">
-        <v>6.315</v>
+        <v>3.859</v>
       </c>
       <c r="R212" s="9" t="n">
-        <v>3897</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="213">
@@ -14931,7 +14933,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -14945,17 +14947,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>9531.T</t>
+          <t>8750.T</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>東京ガス</t>
+          <t>第一生命HD</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>公益</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14964,34 +14966,32 @@
         </is>
       </c>
       <c r="I213" s="4" t="n">
-        <v>7584</v>
+        <v>1421</v>
       </c>
       <c r="J213" s="4" t="n">
-        <v>7609.92</v>
+        <v>1502.86</v>
       </c>
       <c r="K213" s="5" t="n">
-        <v>-0.341</v>
+        <v>-5.447</v>
       </c>
       <c r="L213" s="5" t="n">
         <v>7.45</v>
       </c>
       <c r="M213" s="5" t="n">
-        <v>1.05</v>
+        <v>2.41</v>
       </c>
       <c r="N213" s="5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="O213" t="n">
-        <v>2</v>
-      </c>
+        <v>2.59</v>
+      </c>
+      <c r="O213" t="inlineStr"/>
       <c r="P213" s="7" t="n">
-        <v>3.5</v>
+        <v>11.8</v>
       </c>
       <c r="Q213" s="8" t="n">
-        <v>3.859</v>
+        <v>6.315</v>
       </c>
       <c r="R213" s="9" t="n">
-        <v>6514</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="214">
@@ -15541,7 +15541,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -15555,53 +15555,53 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>9502.T</t>
+          <t>GOOG</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>中部電力</t>
+          <t>Alphabet C</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>公益</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Nikkei225</t>
+          <t>NASDAQ100</t>
         </is>
       </c>
       <c r="I222" s="4" t="n">
-        <v>2517.5</v>
+        <v>301.46</v>
       </c>
       <c r="J222" s="4" t="n">
-        <v>2539.72</v>
+        <v>308.26</v>
       </c>
       <c r="K222" s="5" t="n">
-        <v>-0.875</v>
+        <v>-2.207</v>
       </c>
       <c r="L222" s="5" t="n">
         <v>7.87</v>
       </c>
       <c r="M222" s="5" t="n">
-        <v>2.38</v>
+        <v>0.27</v>
       </c>
       <c r="N222" s="5" t="n">
-        <v>2.57</v>
+        <v>0.29</v>
       </c>
       <c r="O222" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P222" s="7" t="n">
-        <v>6.3</v>
+        <v>12.5</v>
       </c>
       <c r="Q222" s="8" t="n">
-        <v>4.173</v>
+        <v>5.231</v>
       </c>
       <c r="R222" s="9" t="n">
-        <v>6514</v>
+        <v>5402</v>
       </c>
     </row>
     <row r="223">
@@ -15609,7 +15609,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -15623,53 +15623,53 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>9502.T</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Alphabet C</t>
+          <t>中部電力</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>公益</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>NASDAQ100</t>
+          <t>Nikkei225</t>
         </is>
       </c>
       <c r="I223" s="4" t="n">
-        <v>301.46</v>
+        <v>2517.5</v>
       </c>
       <c r="J223" s="4" t="n">
-        <v>308.26</v>
+        <v>2539.72</v>
       </c>
       <c r="K223" s="5" t="n">
-        <v>-2.207</v>
+        <v>-0.875</v>
       </c>
       <c r="L223" s="5" t="n">
         <v>7.87</v>
       </c>
       <c r="M223" s="5" t="n">
-        <v>0.27</v>
+        <v>2.38</v>
       </c>
       <c r="N223" s="5" t="n">
-        <v>0.29</v>
+        <v>2.57</v>
       </c>
       <c r="O223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P223" s="7" t="n">
-        <v>12.5</v>
+        <v>6.3</v>
       </c>
       <c r="Q223" s="8" t="n">
-        <v>5.231</v>
+        <v>4.173</v>
       </c>
       <c r="R223" s="9" t="n">
-        <v>5402</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="224">
@@ -15813,11 +15813,11 @@
         <v>225</v>
       </c>
       <c r="B226" t="n">
-        <v>20</v>
-      </c>
-      <c r="C226" s="11" t="inlineStr">
-        <is>
-          <t>月足陽転</t>
+        <v>25</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D226" s="3" t="inlineStr">
@@ -15827,53 +15827,53 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>2267.T</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>ヤクルト</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>テクノロジー</t>
+          <t>生活必需品</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>NASDAQ100</t>
+          <t>Nikkei225</t>
         </is>
       </c>
       <c r="I226" s="4" t="n">
-        <v>322.16</v>
+        <v>2560</v>
       </c>
       <c r="J226" s="4" t="n">
-        <v>331.2</v>
+        <v>2614.02</v>
       </c>
       <c r="K226" s="5" t="n">
-        <v>-2.729</v>
+        <v>-2.067</v>
       </c>
       <c r="L226" s="5" t="n">
         <v>7.92</v>
       </c>
       <c r="M226" s="5" t="n">
-        <v>0.74</v>
+        <v>2.03</v>
       </c>
       <c r="N226" s="5" t="n">
-        <v>0.79</v>
+        <v>2.19</v>
       </c>
       <c r="O226" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="P226" s="7" t="n">
-        <v>21.8</v>
+        <v>8</v>
+      </c>
+      <c r="P226" s="17" t="n">
+        <v>48.1</v>
       </c>
       <c r="Q226" s="8" t="n">
-        <v>5.782</v>
+        <v>4.811</v>
       </c>
       <c r="R226" s="9" t="n">
-        <v>4152</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="227">
@@ -15881,11 +15881,11 @@
         <v>226</v>
       </c>
       <c r="B227" t="n">
-        <v>25</v>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>20</v>
+      </c>
+      <c r="C227" s="11" t="inlineStr">
+        <is>
+          <t>月足陽転</t>
         </is>
       </c>
       <c r="D227" s="3" t="inlineStr">
@@ -15895,53 +15895,53 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>2267.T</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>ヤクルト</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>生活必需品</t>
+          <t>テクノロジー</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Nikkei225</t>
+          <t>NASDAQ100</t>
         </is>
       </c>
       <c r="I227" s="4" t="n">
-        <v>2560</v>
+        <v>322.16</v>
       </c>
       <c r="J227" s="4" t="n">
-        <v>2614.02</v>
+        <v>331.2</v>
       </c>
       <c r="K227" s="5" t="n">
-        <v>-2.067</v>
+        <v>-2.729</v>
       </c>
       <c r="L227" s="5" t="n">
         <v>7.92</v>
       </c>
       <c r="M227" s="5" t="n">
-        <v>2.03</v>
+        <v>0.74</v>
       </c>
       <c r="N227" s="5" t="n">
-        <v>2.19</v>
+        <v>0.79</v>
       </c>
       <c r="O227" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P227" s="17" t="n">
-        <v>48.1</v>
+        <v>6</v>
+      </c>
+      <c r="P227" s="7" t="n">
+        <v>21.8</v>
       </c>
       <c r="Q227" s="8" t="n">
-        <v>4.811</v>
+        <v>5.782</v>
       </c>
       <c r="R227" s="9" t="n">
-        <v>6255</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="228">
@@ -17299,11 +17299,11 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>25</v>
-      </c>
-      <c r="C248" s="11" t="inlineStr">
-        <is>
-          <t>半値</t>
+        <v>20</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D248" s="3" t="inlineStr">
@@ -17313,17 +17313,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>4043.T</t>
+          <t>1721.T</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>トクヤマ</t>
+          <t>コムシスHD</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -17332,34 +17332,34 @@
         </is>
       </c>
       <c r="I248" s="4" t="n">
-        <v>3854</v>
+        <v>5353</v>
       </c>
       <c r="J248" s="4" t="n">
-        <v>4121.2</v>
+        <v>5419.68</v>
       </c>
       <c r="K248" s="5" t="n">
-        <v>-6.484</v>
+        <v>-1.23</v>
       </c>
       <c r="L248" s="5" t="n">
         <v>8.83</v>
       </c>
       <c r="M248" s="5" t="n">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="N248" s="5" t="n">
-        <v>2.82</v>
+        <v>2.34</v>
       </c>
       <c r="O248" t="n">
         <v>2</v>
       </c>
-      <c r="P248" s="13" t="n">
-        <v>52.6</v>
+      <c r="P248" s="7" t="n">
+        <v>7.1</v>
       </c>
       <c r="Q248" s="8" t="n">
-        <v>7.195</v>
+        <v>4.931</v>
       </c>
       <c r="R248" s="9" t="n">
-        <v>6255</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="249">
@@ -17367,7 +17367,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C249" s="11" t="inlineStr">
         <is>
@@ -17381,51 +17381,53 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>4043.T</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Lululemon</t>
+          <t>トクヤマ</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>NASDAQ100</t>
+          <t>Nikkei225</t>
         </is>
       </c>
       <c r="I249" s="4" t="n">
-        <v>157.78</v>
+        <v>3854</v>
       </c>
       <c r="J249" s="4" t="n">
-        <v>174.97</v>
+        <v>4121.2</v>
       </c>
       <c r="K249" s="5" t="n">
-        <v>-9.826000000000001</v>
+        <v>-6.484</v>
       </c>
       <c r="L249" s="5" t="n">
         <v>8.83</v>
       </c>
       <c r="M249" s="5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="N249" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O249" t="inlineStr"/>
+        <v>2.82</v>
+      </c>
+      <c r="O249" t="n">
+        <v>2</v>
+      </c>
       <c r="P249" s="13" t="n">
-        <v>69.09999999999999</v>
+        <v>52.6</v>
       </c>
       <c r="Q249" s="8" t="n">
-        <v>8.965999999999999</v>
+        <v>7.195</v>
       </c>
       <c r="R249" s="9" t="n">
-        <v>4663</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="250">
@@ -17435,9 +17437,9 @@
       <c r="B250" t="n">
         <v>20</v>
       </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C250" s="11" t="inlineStr">
+        <is>
+          <t>半値</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
@@ -17447,53 +17449,51 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>1721.T</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>コムシスHD</t>
+          <t>Lululemon</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Nikkei225</t>
+          <t>NASDAQ100</t>
         </is>
       </c>
       <c r="I250" s="4" t="n">
-        <v>5353</v>
+        <v>157.78</v>
       </c>
       <c r="J250" s="4" t="n">
-        <v>5419.68</v>
+        <v>174.97</v>
       </c>
       <c r="K250" s="5" t="n">
-        <v>-1.23</v>
+        <v>-9.826000000000001</v>
       </c>
       <c r="L250" s="5" t="n">
         <v>8.83</v>
       </c>
       <c r="M250" s="5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="N250" s="5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="O250" t="n">
-        <v>2</v>
-      </c>
-      <c r="P250" s="7" t="n">
-        <v>7.1</v>
+        <v>0</v>
+      </c>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" s="13" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="Q250" s="8" t="n">
-        <v>4.931</v>
+        <v>8.965999999999999</v>
       </c>
       <c r="R250" s="9" t="n">
-        <v>5540</v>
+        <v>4663</v>
       </c>
     </row>
     <row r="251">
@@ -18579,11 +18579,11 @@
         <v>266</v>
       </c>
       <c r="B267" t="n">
-        <v>10</v>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>20</v>
+      </c>
+      <c r="C267" s="11" t="inlineStr">
+        <is>
+          <t>半値</t>
         </is>
       </c>
       <c r="D267" s="3" t="inlineStr">
@@ -18593,17 +18593,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>6762.T</t>
+          <t>4755.T</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>TDK</t>
+          <t>楽天グループ</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>テクノロジー</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -18612,34 +18612,32 @@
         </is>
       </c>
       <c r="I267" s="4" t="n">
-        <v>2154</v>
+        <v>765.5</v>
       </c>
       <c r="J267" s="4" t="n">
-        <v>2255</v>
+        <v>844.3</v>
       </c>
       <c r="K267" s="5" t="n">
-        <v>-4.479</v>
+        <v>-9.333</v>
       </c>
       <c r="L267" s="5" t="n">
         <v>9.640000000000001</v>
       </c>
       <c r="M267" s="5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="N267" s="5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O267" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P267" s="7" t="n">
-        <v>19.4</v>
+        <v>0</v>
+      </c>
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" s="13" t="n">
+        <v>66.40000000000001</v>
       </c>
       <c r="Q267" s="8" t="n">
-        <v>6.627</v>
+        <v>8.73</v>
       </c>
       <c r="R267" s="9" t="n">
-        <v>6514</v>
+        <v>6438</v>
       </c>
     </row>
     <row r="268">
@@ -18647,11 +18645,11 @@
         <v>267</v>
       </c>
       <c r="B268" t="n">
-        <v>20</v>
-      </c>
-      <c r="C268" s="11" t="inlineStr">
-        <is>
-          <t>半値</t>
+        <v>10</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
@@ -18661,17 +18659,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>4755.T</t>
+          <t>6762.T</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>楽天グループ</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>テクノロジー</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -18680,32 +18678,34 @@
         </is>
       </c>
       <c r="I268" s="4" t="n">
-        <v>765.5</v>
+        <v>2154</v>
       </c>
       <c r="J268" s="4" t="n">
-        <v>844.3</v>
+        <v>2255</v>
       </c>
       <c r="K268" s="5" t="n">
-        <v>-9.333</v>
+        <v>-4.479</v>
       </c>
       <c r="L268" s="5" t="n">
         <v>9.640000000000001</v>
       </c>
       <c r="M268" s="5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="N268" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O268" t="inlineStr"/>
-      <c r="P268" s="13" t="n">
-        <v>66.40000000000001</v>
+        <v>1.53</v>
+      </c>
+      <c r="O268" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P268" s="7" t="n">
+        <v>19.4</v>
       </c>
       <c r="Q268" s="8" t="n">
-        <v>8.73</v>
+        <v>6.627</v>
       </c>
       <c r="R268" s="9" t="n">
-        <v>6438</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="269">
@@ -18795,17 +18795,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>7741.T</t>
+          <t>7762.T</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>HOYA</t>
+          <t>シチズン時計</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>ヘルスケア</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -18814,34 +18814,34 @@
         </is>
       </c>
       <c r="I270" s="4" t="n">
-        <v>27765</v>
+        <v>1634</v>
       </c>
       <c r="J270" s="4" t="n">
-        <v>27843.8</v>
+        <v>1677.2</v>
       </c>
       <c r="K270" s="5" t="n">
-        <v>-0.283</v>
+        <v>-2.576</v>
       </c>
       <c r="L270" s="5" t="n">
         <v>9.84</v>
       </c>
       <c r="M270" s="5" t="n">
-        <v>0.58</v>
+        <v>1.35</v>
       </c>
       <c r="N270" s="5" t="n">
-        <v>0.63</v>
+        <v>1.48</v>
       </c>
       <c r="O270" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P270" s="7" t="n">
-        <v>4.9</v>
+        <v>14.6</v>
       </c>
       <c r="Q270" s="8" t="n">
-        <v>4.917</v>
+        <v>5.818</v>
       </c>
       <c r="R270" s="9" t="n">
-        <v>6255</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="271">
@@ -18863,17 +18863,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>7762.T</t>
+          <t>7741.T</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>シチズン時計</t>
+          <t>HOYA</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>ヘルスケア</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -18882,34 +18882,34 @@
         </is>
       </c>
       <c r="I271" s="4" t="n">
-        <v>1634</v>
+        <v>27765</v>
       </c>
       <c r="J271" s="4" t="n">
-        <v>1677.2</v>
+        <v>27843.8</v>
       </c>
       <c r="K271" s="5" t="n">
-        <v>-2.576</v>
+        <v>-0.283</v>
       </c>
       <c r="L271" s="5" t="n">
         <v>9.84</v>
       </c>
       <c r="M271" s="5" t="n">
-        <v>1.35</v>
+        <v>0.58</v>
       </c>
       <c r="N271" s="5" t="n">
-        <v>1.48</v>
+        <v>0.63</v>
       </c>
       <c r="O271" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P271" s="7" t="n">
-        <v>14.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q271" s="8" t="n">
-        <v>5.818</v>
+        <v>4.917</v>
       </c>
       <c r="R271" s="9" t="n">
-        <v>6514</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="272">
@@ -21085,67 +21085,65 @@
         <v>303</v>
       </c>
       <c r="B304" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D304" s="22" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>MILD DIP</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>VRSK</t>
+          <t>4716.T</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Verisk Analytics</t>
+          <t>日本オラクル(注:代替)</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>テクノロジー</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>NASDAQ100</t>
+          <t>Nikkei225</t>
         </is>
       </c>
       <c r="I304" s="4" t="n">
-        <v>201.22</v>
+        <v>9325</v>
       </c>
       <c r="J304" s="4" t="n">
-        <v>193.68</v>
+        <v>9450.84</v>
       </c>
       <c r="K304" s="5" t="n">
-        <v>3.891</v>
+        <v>-1.332</v>
       </c>
       <c r="L304" s="5" t="n">
         <v>11.12</v>
       </c>
       <c r="M304" s="5" t="n">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="N304" s="5" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="O304" s="2" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O304" t="inlineStr"/>
       <c r="P304" s="17" t="n">
-        <v>36.9</v>
+        <v>47.6</v>
       </c>
       <c r="Q304" s="8" t="n">
-        <v>3.566</v>
+        <v>5.638</v>
       </c>
       <c r="R304" s="9" t="n">
-        <v>4109</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="305">
@@ -21153,65 +21151,67 @@
         <v>304</v>
       </c>
       <c r="B305" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D305" s="3" t="inlineStr">
-        <is>
-          <t>MILD DIP</t>
+      <c r="D305" s="22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>4716.T</t>
+          <t>VRSK</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>日本オラクル(注:代替)</t>
+          <t>Verisk Analytics</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>テクノロジー</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Nikkei225</t>
+          <t>NASDAQ100</t>
         </is>
       </c>
       <c r="I305" s="4" t="n">
-        <v>9325</v>
+        <v>201.22</v>
       </c>
       <c r="J305" s="4" t="n">
-        <v>9450.84</v>
+        <v>193.68</v>
       </c>
       <c r="K305" s="5" t="n">
-        <v>-1.332</v>
+        <v>3.891</v>
       </c>
       <c r="L305" s="5" t="n">
         <v>11.12</v>
       </c>
       <c r="M305" s="5" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="N305" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O305" t="inlineStr"/>
+        <v>0.99</v>
+      </c>
+      <c r="O305" s="2" t="n">
+        <v>6</v>
+      </c>
       <c r="P305" s="17" t="n">
-        <v>47.6</v>
+        <v>36.9</v>
       </c>
       <c r="Q305" s="8" t="n">
-        <v>5.638</v>
+        <v>3.566</v>
       </c>
       <c r="R305" s="9" t="n">
-        <v>6252</v>
+        <v>4109</v>
       </c>
     </row>
     <row r="306">
@@ -21233,53 +21233,53 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>8002.T</t>
+          <t>CSCO</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>丸紅</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>テクノロジー</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Nikkei225</t>
+          <t>Dow30</t>
         </is>
       </c>
       <c r="I306" s="4" t="n">
-        <v>5591</v>
+        <v>78.33</v>
       </c>
       <c r="J306" s="4" t="n">
-        <v>5720.04</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="K306" s="5" t="n">
-        <v>-2.256</v>
+        <v>-1.428</v>
       </c>
       <c r="L306" s="5" t="n">
         <v>11.17</v>
       </c>
       <c r="M306" s="5" t="n">
-        <v>1.7</v>
+        <v>2.08</v>
       </c>
       <c r="N306" s="5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="O306" s="2" t="n">
-        <v>5</v>
+        <v>2.31</v>
+      </c>
+      <c r="O306" s="16" t="n">
+        <v>14</v>
       </c>
       <c r="P306" s="7" t="n">
-        <v>11.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q306" s="8" t="n">
-        <v>6.394</v>
+        <v>6.197</v>
       </c>
       <c r="R306" s="9" t="n">
-        <v>6514</v>
+        <v>9059</v>
       </c>
     </row>
     <row r="307">
@@ -21301,53 +21301,53 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>CSCO</t>
+          <t>8002.T</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>丸紅</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>テクノロジー</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Dow30</t>
+          <t>Nikkei225</t>
         </is>
       </c>
       <c r="I307" s="4" t="n">
-        <v>78.33</v>
+        <v>5591</v>
       </c>
       <c r="J307" s="4" t="n">
-        <v>79.45999999999999</v>
+        <v>5720.04</v>
       </c>
       <c r="K307" s="5" t="n">
-        <v>-1.428</v>
+        <v>-2.256</v>
       </c>
       <c r="L307" s="5" t="n">
         <v>11.17</v>
       </c>
       <c r="M307" s="5" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="N307" s="5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="O307" s="16" t="n">
-        <v>14</v>
+        <v>1.89</v>
+      </c>
+      <c r="O307" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="P307" s="7" t="n">
-        <v>9.699999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="Q307" s="8" t="n">
-        <v>6.197</v>
+        <v>6.394</v>
       </c>
       <c r="R307" s="9" t="n">
-        <v>9059</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="308">
@@ -23456,19 +23456,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D339" s="3" t="inlineStr">
-        <is>
-          <t>MILD DIP</t>
+      <c r="D339" s="22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -23482,32 +23482,34 @@
         </is>
       </c>
       <c r="I339" s="4" t="n">
-        <v>161.36</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="J339" s="4" t="n">
-        <v>173.19</v>
+        <v>97.67</v>
       </c>
       <c r="K339" s="5" t="n">
-        <v>-6.833</v>
+        <v>1.512</v>
       </c>
       <c r="L339" s="5" t="n">
         <v>13.77</v>
       </c>
       <c r="M339" s="5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="N339" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O339" t="inlineStr"/>
-      <c r="P339" s="17" t="n">
-        <v>42.7</v>
+        <v>2.81</v>
+      </c>
+      <c r="O339" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P339" s="7" t="n">
+        <v>12.1</v>
       </c>
       <c r="Q339" s="8" t="n">
-        <v>9.194000000000001</v>
+        <v>5.835</v>
       </c>
       <c r="R339" s="9" t="n">
-        <v>1296</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="340">
@@ -23522,19 +23524,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D340" s="22" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>MILD DIP</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -23548,34 +23550,32 @@
         </is>
       </c>
       <c r="I340" s="4" t="n">
-        <v>99.15000000000001</v>
+        <v>161.36</v>
       </c>
       <c r="J340" s="4" t="n">
-        <v>97.67</v>
+        <v>173.19</v>
       </c>
       <c r="K340" s="5" t="n">
-        <v>1.512</v>
+        <v>-6.833</v>
       </c>
       <c r="L340" s="5" t="n">
         <v>13.77</v>
       </c>
       <c r="M340" s="5" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="N340" s="5" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="O340" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="P340" s="7" t="n">
-        <v>12.1</v>
+        <v>0</v>
+      </c>
+      <c r="O340" t="inlineStr"/>
+      <c r="P340" s="17" t="n">
+        <v>42.7</v>
       </c>
       <c r="Q340" s="8" t="n">
-        <v>5.835</v>
+        <v>9.194000000000001</v>
       </c>
       <c r="R340" s="9" t="n">
-        <v>8463</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="341">
@@ -24393,65 +24393,67 @@
         <v>352</v>
       </c>
       <c r="B353" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D353" s="3" t="inlineStr">
-        <is>
-          <t>MILD DIP</t>
+      <c r="D353" s="22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>ABNB</t>
+          <t>5019.T</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>出光興産</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>エネルギー</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>NASDAQ100</t>
+          <t>Nikkei225</t>
         </is>
       </c>
       <c r="I353" s="4" t="n">
-        <v>126.3</v>
+        <v>1462</v>
       </c>
       <c r="J353" s="4" t="n">
-        <v>128.01</v>
+        <v>1423.38</v>
       </c>
       <c r="K353" s="5" t="n">
-        <v>-1.34</v>
+        <v>2.713</v>
       </c>
       <c r="L353" s="5" t="n">
         <v>15.52</v>
       </c>
       <c r="M353" s="5" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="N353" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O353" t="inlineStr"/>
-      <c r="P353" s="17" t="n">
-        <v>41.8</v>
+        <v>2.84</v>
+      </c>
+      <c r="O353" t="n">
+        <v>2</v>
+      </c>
+      <c r="P353" s="7" t="n">
+        <v>3.7</v>
       </c>
       <c r="Q353" s="8" t="n">
-        <v>7.28</v>
+        <v>5.775</v>
       </c>
       <c r="R353" s="9" t="n">
-        <v>1295</v>
+        <v>4739</v>
       </c>
     </row>
     <row r="354">
@@ -24459,67 +24461,65 @@
         <v>353</v>
       </c>
       <c r="B354" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D354" s="22" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="D354" s="3" t="inlineStr">
+        <is>
+          <t>MILD DIP</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>5019.T</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>出光興産</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>エネルギー</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Nikkei225</t>
+          <t>NASDAQ100</t>
         </is>
       </c>
       <c r="I354" s="4" t="n">
-        <v>1462</v>
+        <v>126.3</v>
       </c>
       <c r="J354" s="4" t="n">
-        <v>1423.38</v>
+        <v>128.01</v>
       </c>
       <c r="K354" s="5" t="n">
-        <v>2.713</v>
+        <v>-1.34</v>
       </c>
       <c r="L354" s="5" t="n">
         <v>15.52</v>
       </c>
       <c r="M354" s="5" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="N354" s="5" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O354" t="n">
-        <v>2</v>
-      </c>
-      <c r="P354" s="7" t="n">
-        <v>3.7</v>
+        <v>0</v>
+      </c>
+      <c r="O354" t="inlineStr"/>
+      <c r="P354" s="17" t="n">
+        <v>41.8</v>
       </c>
       <c r="Q354" s="8" t="n">
-        <v>5.775</v>
+        <v>7.28</v>
       </c>
       <c r="R354" s="9" t="n">
-        <v>4739</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="355">
@@ -29197,7 +29197,7 @@
         <v>9.6</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>816.574</v>
+        <v>816.576</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>6514</v>
@@ -31573,8 +31573,8 @@
       <c r="A38" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="14" t="n">
-        <v>50</v>
+      <c r="B38" s="2" t="n">
+        <v>35</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -31588,17 +31588,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>9007.T</t>
+          <t>6473.T</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>小田急電鉄</t>
+          <t>ジェイテクト</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -31607,31 +31607,31 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>1631.5</v>
+        <v>1750</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>1720.3</v>
+        <v>1967.52</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-5.162</v>
+        <v>-11.056</v>
       </c>
       <c r="L38" s="20" t="n">
         <v>2.2</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="N38" s="5" t="n">
-        <v>2.51</v>
+        <v>2.92</v>
       </c>
       <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" s="17" t="n">
-        <v>49.2</v>
+        <v>4</v>
+      </c>
+      <c r="P38" s="7" t="n">
+        <v>18.6</v>
       </c>
       <c r="Q38" s="8" t="n">
-        <v>3.732</v>
+        <v>6.658</v>
       </c>
       <c r="R38" s="9" t="n">
         <v>6514</v>
@@ -31641,8 +31641,8 @@
       <c r="A39" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="n">
-        <v>35</v>
+      <c r="B39" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -31656,17 +31656,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6473.T</t>
+          <t>9007.T</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ジェイテクト</t>
+          <t>小田急電鉄</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -31675,31 +31675,31 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>1750</v>
+        <v>1631.5</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>1967.52</v>
+        <v>1720.3</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>-11.056</v>
+        <v>-5.162</v>
       </c>
       <c r="L39" s="20" t="n">
         <v>2.2</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
       <c r="N39" s="5" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
-      </c>
-      <c r="P39" s="7" t="n">
-        <v>18.6</v>
+        <v>3</v>
+      </c>
+      <c r="P39" s="17" t="n">
+        <v>49.2</v>
       </c>
       <c r="Q39" s="8" t="n">
-        <v>6.658</v>
+        <v>3.732</v>
       </c>
       <c r="R39" s="9" t="n">
         <v>6514</v>
@@ -32186,7 +32186,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -32200,17 +32200,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8267.T</t>
+          <t>1332.T</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>イオン</t>
+          <t>日本水産</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>生活必需品</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -32219,31 +32219,31 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>2019</v>
+        <v>1354</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>2185.33</v>
+        <v>1467.9</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-7.611</v>
+        <v>-7.759</v>
       </c>
       <c r="L47" s="20" t="n">
         <v>2.85</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>0.66</v>
+        <v>2.07</v>
       </c>
       <c r="N47" s="5" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="O47" t="n">
-        <v>2</v>
+        <v>2.13</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="P47" s="7" t="n">
-        <v>29.6</v>
+        <v>13.2</v>
       </c>
       <c r="Q47" s="8" t="n">
-        <v>5.332</v>
+        <v>5.433</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>6514</v>
@@ -32254,7 +32254,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -32268,17 +32268,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1332.T</t>
+          <t>8267.T</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>日本水産</t>
+          <t>イオン</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>生活必需品</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -32287,31 +32287,31 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>1354</v>
+        <v>2019</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>1467.9</v>
+        <v>2185.33</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-7.759</v>
+        <v>-7.611</v>
       </c>
       <c r="L48" s="20" t="n">
         <v>2.85</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>2.07</v>
+        <v>0.66</v>
       </c>
       <c r="N48" s="5" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="O48" s="2" t="n">
-        <v>6</v>
+        <v>0.68</v>
+      </c>
+      <c r="O48" t="n">
+        <v>2</v>
       </c>
       <c r="P48" s="7" t="n">
-        <v>13.2</v>
+        <v>29.6</v>
       </c>
       <c r="Q48" s="8" t="n">
-        <v>5.433</v>
+        <v>5.332</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>6514</v>
@@ -32940,17 +32940,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2502.T</t>
+          <t>5201.T</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>アサヒGHD</t>
+          <t>AGC</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>生活必需品</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -32959,31 +32959,29 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>1600</v>
+        <v>5830</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>1672.24</v>
+        <v>6292.48</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-4.32</v>
+        <v>-7.35</v>
       </c>
       <c r="L58" s="5" t="n">
         <v>3.87</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="O58" s="16" t="n">
-        <v>23</v>
-      </c>
+        <v>3.74</v>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" s="7" t="n">
-        <v>18.8</v>
+        <v>15.9</v>
       </c>
       <c r="Q58" s="8" t="n">
-        <v>4.145</v>
+        <v>5.534</v>
       </c>
       <c r="R58" s="9" t="n">
         <v>6514</v>
@@ -33008,17 +33006,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5201.T</t>
+          <t>2502.T</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AGC</t>
+          <t>アサヒGHD</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>生活必需品</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -33027,29 +33025,31 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>5830</v>
+        <v>1600</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>6292.48</v>
+        <v>1672.24</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>-7.35</v>
+        <v>-4.32</v>
       </c>
       <c r="L59" s="5" t="n">
         <v>3.87</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="O59" t="inlineStr"/>
+        <v>3.18</v>
+      </c>
+      <c r="O59" s="16" t="n">
+        <v>23</v>
+      </c>
       <c r="P59" s="7" t="n">
-        <v>15.9</v>
+        <v>18.8</v>
       </c>
       <c r="Q59" s="8" t="n">
-        <v>5.534</v>
+        <v>4.145</v>
       </c>
       <c r="R59" s="9" t="n">
         <v>6514</v>
@@ -33680,17 +33680,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>6471.T</t>
+          <t>2501.T</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>日本精工</t>
+          <t>サッポロHD</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>生活必需品</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -33699,31 +33699,31 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>1169.5</v>
+        <v>1612</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>1279.48</v>
+        <v>1720.88</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-8.596</v>
+        <v>-6.327</v>
       </c>
       <c r="L69" s="5" t="n">
         <v>4.68</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>2.91</v>
+        <v>1.12</v>
       </c>
       <c r="N69" s="5" t="n">
-        <v>3.04</v>
+        <v>1.17</v>
       </c>
       <c r="O69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P69" s="7" t="n">
-        <v>20.3</v>
+        <v>14.3</v>
       </c>
       <c r="Q69" s="8" t="n">
-        <v>6.493</v>
+        <v>5.475</v>
       </c>
       <c r="R69" s="9" t="n">
         <v>6514</v>
@@ -33748,17 +33748,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2501.T</t>
+          <t>6471.T</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>サッポロHD</t>
+          <t>日本精工</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>生活必需品</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -33767,31 +33767,31 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>1612</v>
+        <v>1169.5</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>1720.88</v>
+        <v>1279.48</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-6.327</v>
+        <v>-8.596</v>
       </c>
       <c r="L70" s="5" t="n">
         <v>4.68</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>1.12</v>
+        <v>2.91</v>
       </c>
       <c r="N70" s="5" t="n">
-        <v>1.17</v>
+        <v>3.04</v>
       </c>
       <c r="O70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P70" s="7" t="n">
-        <v>14.3</v>
+        <v>20.3</v>
       </c>
       <c r="Q70" s="8" t="n">
-        <v>5.475</v>
+        <v>6.493</v>
       </c>
       <c r="R70" s="9" t="n">
         <v>6514</v>
@@ -34758,17 +34758,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>3861.T</t>
+          <t>9020.T</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>王子HD</t>
+          <t>東日本旅客鉄道</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -34777,31 +34777,31 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>908.2</v>
+        <v>3721</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>952.6799999999999</v>
+        <v>3810.16</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-4.669</v>
+        <v>-2.34</v>
       </c>
       <c r="L85" s="5" t="n">
         <v>5.35</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>2.64</v>
+        <v>1.61</v>
       </c>
       <c r="N85" s="5" t="n">
-        <v>2.78</v>
+        <v>1.7</v>
       </c>
       <c r="O85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P85" s="7" t="n">
-        <v>8.1</v>
+        <v>11.4</v>
       </c>
       <c r="Q85" s="8" t="n">
-        <v>4.871</v>
+        <v>3.773</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>6514</v>
@@ -34826,17 +34826,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>9020.T</t>
+          <t>3861.T</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>東日本旅客鉄道</t>
+          <t>王子HD</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -34845,31 +34845,31 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>3721</v>
+        <v>908.2</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>3810.16</v>
+        <v>952.6799999999999</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-2.34</v>
+        <v>-4.669</v>
       </c>
       <c r="L86" s="5" t="n">
         <v>5.35</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>1.61</v>
+        <v>2.64</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>1.7</v>
+        <v>2.78</v>
       </c>
       <c r="O86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P86" s="7" t="n">
-        <v>11.4</v>
+        <v>8.1</v>
       </c>
       <c r="Q86" s="8" t="n">
-        <v>3.773</v>
+        <v>4.871</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>6514</v>
@@ -34880,7 +34880,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -34894,17 +34894,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>7752.T</t>
+          <t>5301.T</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>リコー</t>
+          <t>東海カーボン</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -34913,34 +34913,32 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>1347.5</v>
+        <v>959.7</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>1434.8</v>
+        <v>1046.57</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-6.084</v>
+        <v>-8.301</v>
       </c>
       <c r="L87" s="5" t="n">
         <v>5.41</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>2.82</v>
+        <v>3.13</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="O87" t="n">
-        <v>4</v>
-      </c>
-      <c r="P87" s="7" t="n">
-        <v>24.8</v>
+        <v>3.3</v>
+      </c>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" s="17" t="n">
+        <v>48.3</v>
       </c>
       <c r="Q87" s="8" t="n">
-        <v>5.541</v>
+        <v>6.765</v>
       </c>
       <c r="R87" s="9" t="n">
-        <v>6687</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="88">
@@ -34948,7 +34946,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -34962,17 +34960,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>5301.T</t>
+          <t>7752.T</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>東海カーボン</t>
+          <t>リコー</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -34981,32 +34979,34 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>959.7</v>
+        <v>1347.5</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>1046.57</v>
+        <v>1434.8</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-8.301</v>
+        <v>-6.084</v>
       </c>
       <c r="L88" s="5" t="n">
         <v>5.41</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>3.13</v>
+        <v>2.82</v>
       </c>
       <c r="N88" s="5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" s="17" t="n">
-        <v>48.3</v>
+        <v>2.97</v>
+      </c>
+      <c r="O88" t="n">
+        <v>4</v>
+      </c>
+      <c r="P88" s="7" t="n">
+        <v>24.8</v>
       </c>
       <c r="Q88" s="8" t="n">
-        <v>6.765</v>
+        <v>5.541</v>
       </c>
       <c r="R88" s="9" t="n">
-        <v>6514</v>
+        <v>6687</v>
       </c>
     </row>
     <row r="89">
@@ -36780,17 +36780,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>3659.T</t>
+          <t>3088.T</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>ネクソン</t>
+          <t>マツキヨココカラ</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>通信</t>
+          <t>ヘルスケア</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -36799,34 +36799,34 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3012</v>
+        <v>2463</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>3242.76</v>
+        <v>2552.58</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>-7.116</v>
+        <v>-3.509</v>
       </c>
       <c r="L115" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>1.49</v>
+        <v>1.79</v>
       </c>
       <c r="N115" s="5" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="O115" t="n">
-        <v>2</v>
-      </c>
-      <c r="P115" s="17" t="n">
-        <v>31.9</v>
+        <v>4</v>
+      </c>
+      <c r="P115" s="7" t="n">
+        <v>26.7</v>
       </c>
       <c r="Q115" s="8" t="n">
-        <v>6.906</v>
+        <v>5.143</v>
       </c>
       <c r="R115" s="9" t="n">
-        <v>3481</v>
+        <v>6252</v>
       </c>
     </row>
     <row r="116">
@@ -36848,17 +36848,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>3088.T</t>
+          <t>3659.T</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>マツキヨココカラ</t>
+          <t>ネクソン</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>ヘルスケア</t>
+          <t>通信</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -36867,34 +36867,34 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>2463</v>
+        <v>3012</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>2552.58</v>
+        <v>3242.76</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>-3.509</v>
+        <v>-7.116</v>
       </c>
       <c r="L116" s="5" t="n">
         <v>6.89</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="N116" s="5" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="O116" t="n">
-        <v>4</v>
-      </c>
-      <c r="P116" s="7" t="n">
-        <v>26.7</v>
+        <v>2</v>
+      </c>
+      <c r="P116" s="17" t="n">
+        <v>31.9</v>
       </c>
       <c r="Q116" s="8" t="n">
-        <v>5.143</v>
+        <v>6.906</v>
       </c>
       <c r="R116" s="9" t="n">
-        <v>6252</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="117">
@@ -37574,7 +37574,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -37588,17 +37588,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>8750.T</t>
+          <t>9531.T</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>第一生命HD</t>
+          <t>東京ガス</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>公益</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -37607,32 +37607,34 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>1421</v>
+        <v>7584</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>1502.86</v>
+        <v>7609.92</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>-5.447</v>
+        <v>-0.341</v>
       </c>
       <c r="L127" s="5" t="n">
         <v>7.45</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>2.41</v>
+        <v>1.05</v>
       </c>
       <c r="N127" s="5" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O127" t="inlineStr"/>
+        <v>1.13</v>
+      </c>
+      <c r="O127" t="n">
+        <v>2</v>
+      </c>
       <c r="P127" s="7" t="n">
-        <v>11.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q127" s="8" t="n">
-        <v>6.315</v>
+        <v>3.859</v>
       </c>
       <c r="R127" s="9" t="n">
-        <v>3897</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="128">
@@ -37640,7 +37642,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -37654,17 +37656,17 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>9531.T</t>
+          <t>8750.T</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>東京ガス</t>
+          <t>第一生命HD</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>公益</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -37673,34 +37675,32 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>7584</v>
+        <v>1421</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>7609.92</v>
+        <v>1502.86</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>-0.341</v>
+        <v>-5.447</v>
       </c>
       <c r="L128" s="5" t="n">
         <v>7.45</v>
       </c>
       <c r="M128" s="5" t="n">
-        <v>1.05</v>
+        <v>2.41</v>
       </c>
       <c r="N128" s="5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="O128" t="n">
-        <v>2</v>
-      </c>
+        <v>2.59</v>
+      </c>
+      <c r="O128" t="inlineStr"/>
       <c r="P128" s="7" t="n">
-        <v>3.5</v>
+        <v>11.8</v>
       </c>
       <c r="Q128" s="8" t="n">
-        <v>3.859</v>
+        <v>6.315</v>
       </c>
       <c r="R128" s="9" t="n">
-        <v>6514</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="129">
@@ -39268,11 +39268,11 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>25</v>
-      </c>
-      <c r="C152" s="11" t="inlineStr">
-        <is>
-          <t>半値</t>
+        <v>20</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
@@ -39282,17 +39282,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>4043.T</t>
+          <t>1721.T</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>トクヤマ</t>
+          <t>コムシスHD</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -39301,34 +39301,34 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>3854</v>
+        <v>5353</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>4121.2</v>
+        <v>5419.68</v>
       </c>
       <c r="K152" s="5" t="n">
-        <v>-6.484</v>
+        <v>-1.23</v>
       </c>
       <c r="L152" s="5" t="n">
         <v>8.83</v>
       </c>
       <c r="M152" s="5" t="n">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="N152" s="5" t="n">
-        <v>2.82</v>
+        <v>2.34</v>
       </c>
       <c r="O152" t="n">
         <v>2</v>
       </c>
-      <c r="P152" s="13" t="n">
-        <v>52.6</v>
+      <c r="P152" s="7" t="n">
+        <v>7.1</v>
       </c>
       <c r="Q152" s="8" t="n">
-        <v>7.195</v>
+        <v>4.931</v>
       </c>
       <c r="R152" s="9" t="n">
-        <v>6255</v>
+        <v>5540</v>
       </c>
     </row>
     <row r="153">
@@ -39336,11 +39336,11 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>20</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>25</v>
+      </c>
+      <c r="C153" s="11" t="inlineStr">
+        <is>
+          <t>半値</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
@@ -39350,17 +39350,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>1721.T</t>
+          <t>4043.T</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>コムシスHD</t>
+          <t>トクヤマ</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -39369,34 +39369,34 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>5353</v>
+        <v>3854</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>5419.68</v>
+        <v>4121.2</v>
       </c>
       <c r="K153" s="5" t="n">
-        <v>-1.23</v>
+        <v>-6.484</v>
       </c>
       <c r="L153" s="5" t="n">
         <v>8.83</v>
       </c>
       <c r="M153" s="5" t="n">
-        <v>2.15</v>
+        <v>2.59</v>
       </c>
       <c r="N153" s="5" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="O153" t="n">
         <v>2</v>
       </c>
-      <c r="P153" s="7" t="n">
-        <v>7.1</v>
+      <c r="P153" s="13" t="n">
+        <v>52.6</v>
       </c>
       <c r="Q153" s="8" t="n">
-        <v>4.931</v>
+        <v>7.195</v>
       </c>
       <c r="R153" s="9" t="n">
-        <v>5540</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="154">
@@ -40076,11 +40076,11 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>10</v>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>—</t>
+        <v>20</v>
+      </c>
+      <c r="C164" s="11" t="inlineStr">
+        <is>
+          <t>半値</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
@@ -40090,17 +40090,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>6762.T</t>
+          <t>4755.T</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>TDK</t>
+          <t>楽天グループ</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>テクノロジー</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -40109,34 +40109,32 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>2154</v>
+        <v>765.5</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>2255</v>
+        <v>844.3</v>
       </c>
       <c r="K164" s="5" t="n">
-        <v>-4.479</v>
+        <v>-9.333</v>
       </c>
       <c r="L164" s="5" t="n">
         <v>9.640000000000001</v>
       </c>
       <c r="M164" s="5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="N164" s="5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O164" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P164" s="7" t="n">
-        <v>19.4</v>
+        <v>0</v>
+      </c>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" s="13" t="n">
+        <v>66.40000000000001</v>
       </c>
       <c r="Q164" s="8" t="n">
-        <v>6.627</v>
+        <v>8.73</v>
       </c>
       <c r="R164" s="9" t="n">
-        <v>6514</v>
+        <v>6438</v>
       </c>
     </row>
     <row r="165">
@@ -40144,11 +40142,11 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>20</v>
-      </c>
-      <c r="C165" s="11" t="inlineStr">
-        <is>
-          <t>半値</t>
+        <v>10</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="D165" s="3" t="inlineStr">
@@ -40158,17 +40156,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>4755.T</t>
+          <t>6762.T</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>楽天グループ</t>
+          <t>TDK</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>テクノロジー</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -40177,32 +40175,34 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>765.5</v>
+        <v>2154</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>844.3</v>
+        <v>2255</v>
       </c>
       <c r="K165" s="5" t="n">
-        <v>-9.333</v>
+        <v>-4.479</v>
       </c>
       <c r="L165" s="5" t="n">
         <v>9.640000000000001</v>
       </c>
       <c r="M165" s="5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="N165" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" s="13" t="n">
-        <v>66.40000000000001</v>
+        <v>1.53</v>
+      </c>
+      <c r="O165" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P165" s="7" t="n">
+        <v>19.4</v>
       </c>
       <c r="Q165" s="8" t="n">
-        <v>8.73</v>
+        <v>6.627</v>
       </c>
       <c r="R165" s="9" t="n">
-        <v>6438</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="166">
@@ -40292,17 +40292,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>7741.T</t>
+          <t>7762.T</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>HOYA</t>
+          <t>シチズン時計</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>ヘルスケア</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -40311,34 +40311,34 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>27765</v>
+        <v>1634</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>27843.8</v>
+        <v>1677.2</v>
       </c>
       <c r="K167" s="5" t="n">
-        <v>-0.283</v>
+        <v>-2.576</v>
       </c>
       <c r="L167" s="5" t="n">
         <v>9.84</v>
       </c>
       <c r="M167" s="5" t="n">
-        <v>0.58</v>
+        <v>1.35</v>
       </c>
       <c r="N167" s="5" t="n">
-        <v>0.63</v>
+        <v>1.48</v>
       </c>
       <c r="O167" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P167" s="7" t="n">
-        <v>4.9</v>
+        <v>14.6</v>
       </c>
       <c r="Q167" s="8" t="n">
-        <v>4.917</v>
+        <v>5.818</v>
       </c>
       <c r="R167" s="9" t="n">
-        <v>6255</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="168">
@@ -40360,17 +40360,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>7762.T</t>
+          <t>7741.T</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>シチズン時計</t>
+          <t>HOYA</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>ヘルスケア</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -40379,34 +40379,34 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>1634</v>
+        <v>27765</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>1677.2</v>
+        <v>27843.8</v>
       </c>
       <c r="K168" s="5" t="n">
-        <v>-2.576</v>
+        <v>-0.283</v>
       </c>
       <c r="L168" s="5" t="n">
         <v>9.84</v>
       </c>
       <c r="M168" s="5" t="n">
-        <v>1.35</v>
+        <v>0.58</v>
       </c>
       <c r="N168" s="5" t="n">
-        <v>1.48</v>
+        <v>0.63</v>
       </c>
       <c r="O168" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P168" s="7" t="n">
-        <v>14.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q168" s="8" t="n">
-        <v>5.818</v>
+        <v>4.917</v>
       </c>
       <c r="R168" s="9" t="n">
-        <v>6514</v>
+        <v>6255</v>
       </c>
     </row>
     <row r="169">
@@ -45942,7 +45942,7 @@
         <v>13.3</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>3.407</v>
+        <v>3.406</v>
       </c>
       <c r="R6" s="9" t="n">
         <v>16133</v>
@@ -51545,19 +51545,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>MILD DIP</t>
+      <c r="D58" s="22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -51571,32 +51571,34 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>161.36</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>173.19</v>
+        <v>97.67</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-6.833</v>
+        <v>1.512</v>
       </c>
       <c r="L58" s="5" t="n">
         <v>13.77</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" s="17" t="n">
-        <v>42.7</v>
+        <v>2.81</v>
+      </c>
+      <c r="O58" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="P58" s="7" t="n">
+        <v>12.1</v>
       </c>
       <c r="Q58" s="8" t="n">
-        <v>9.194000000000001</v>
+        <v>5.835</v>
       </c>
       <c r="R58" s="9" t="n">
-        <v>1296</v>
+        <v>8463</v>
       </c>
     </row>
     <row r="59">
@@ -51611,19 +51613,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D59" s="22" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>MILD DIP</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>DASH</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -51637,34 +51639,32 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>99.15000000000001</v>
+        <v>161.36</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>97.67</v>
+        <v>173.19</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>1.512</v>
+        <v>-6.833</v>
       </c>
       <c r="L59" s="5" t="n">
         <v>13.77</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="N59" s="5" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="O59" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="P59" s="7" t="n">
-        <v>12.1</v>
+        <v>0</v>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" s="17" t="n">
+        <v>42.7</v>
       </c>
       <c r="Q59" s="8" t="n">
-        <v>5.835</v>
+        <v>9.194000000000001</v>
       </c>
       <c r="R59" s="9" t="n">
-        <v>8463</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="60">
@@ -58035,7 +58035,7 @@
         <v>9.6</v>
       </c>
       <c r="Q2" s="8" t="n">
-        <v>816.574</v>
+        <v>816.576</v>
       </c>
       <c r="R2" s="9" t="n">
         <v>6514</v>
@@ -61696,7 +61696,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -61710,53 +61710,53 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>素材</t>
+          <t>生活必需品</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>配当貴族</t>
+          <t>Dow30</t>
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>274.18</v>
+        <v>150.65</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>295.53</v>
+        <v>158.89</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-7.225</v>
+        <v>-5.186</v>
       </c>
       <c r="L57" s="20" t="n">
         <v>1.19</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>1.21</v>
+        <v>2.7</v>
       </c>
       <c r="N57" s="5" t="n">
-        <v>1.23</v>
+        <v>2.73</v>
       </c>
       <c r="O57" s="16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P57" s="7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="Q57" s="8" t="n">
-        <v>4.421</v>
+        <v>3.406</v>
       </c>
       <c r="R57" s="9" t="n">
-        <v>13354</v>
+        <v>16133</v>
       </c>
     </row>
     <row r="58">
@@ -61764,7 +61764,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -61778,53 +61778,53 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>ECL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>生活必需品</t>
+          <t>素材</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Dow30</t>
+          <t>配当貴族</t>
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>150.65</v>
+        <v>274.18</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>158.89</v>
+        <v>295.53</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-5.186</v>
+        <v>-7.225</v>
       </c>
       <c r="L58" s="20" t="n">
         <v>1.19</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>2.7</v>
+        <v>1.21</v>
       </c>
       <c r="N58" s="5" t="n">
-        <v>2.73</v>
+        <v>1.23</v>
       </c>
       <c r="O58" s="16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P58" s="7" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="Q58" s="8" t="n">
-        <v>3.407</v>
+        <v>4.421</v>
       </c>
       <c r="R58" s="9" t="n">
-        <v>16133</v>
+        <v>13354</v>
       </c>
     </row>
     <row r="59">
@@ -62376,7 +62376,7 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -62390,53 +62390,53 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CHRW</t>
+          <t>4151.T</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>協和キリン</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>ヘルスケア</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>配当貴族</t>
+          <t>Nikkei225</t>
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>169.39</v>
+        <v>2331</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>182.94</v>
+        <v>2531.08</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-7.408</v>
+        <v>-7.905</v>
       </c>
       <c r="L67" s="20" t="n">
         <v>1.75</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>1.84</v>
+        <v>2.66</v>
       </c>
       <c r="N67" s="5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="O67" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="P67" s="7" t="n">
-        <v>15.3</v>
+        <v>2.71</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="P67" s="17" t="n">
+        <v>39.2</v>
       </c>
       <c r="Q67" s="8" t="n">
-        <v>4.86</v>
+        <v>4.886</v>
       </c>
       <c r="R67" s="9" t="n">
-        <v>7121</v>
+        <v>6514</v>
       </c>
     </row>
     <row r="68">
@@ -62444,7 +62444,7 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -62458,53 +62458,53 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>4151.T</t>
+          <t>CHRW</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>協和キリン</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>ヘルスケア</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Nikkei225</t>
+          <t>配当貴族</t>
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>2331</v>
+        <v>169.39</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>2531.08</v>
+        <v>182.94</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-7.905</v>
+        <v>-7.408</v>
       </c>
       <c r="L68" s="20" t="n">
         <v>1.75</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>2.66</v>
+        <v>1.84</v>
       </c>
       <c r="N68" s="5" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="O68" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="P68" s="17" t="n">
-        <v>39.2</v>
+        <v>1.87</v>
+      </c>
+      <c r="O68" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="P68" s="7" t="n">
+        <v>15.3</v>
       </c>
       <c r="Q68" s="8" t="n">
-        <v>4.886</v>
+        <v>4.86</v>
       </c>
       <c r="R68" s="9" t="n">
-        <v>6514</v>
+        <v>7121</v>
       </c>
     </row>
     <row r="69">
@@ -62713,8 +62713,8 @@
       <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="14" t="n">
-        <v>50</v>
+      <c r="B72" s="2" t="n">
+        <v>35</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -62728,17 +62728,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>9007.T</t>
+          <t>6473.T</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>小田急電鉄</t>
+          <t>ジェイテクト</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>資本財</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -62747,31 +62747,31 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>1631.5</v>
+        <v>1750</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>1720.3</v>
+        <v>1967.52</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-5.162</v>
+        <v>-11.056</v>
       </c>
       <c r="L72" s="20" t="n">
         <v>2.2</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>2.45</v>
+        <v>2.86</v>
       </c>
       <c r="N72" s="5" t="n">
-        <v>2.51</v>
+        <v>2.92</v>
       </c>
       <c r="O72" t="n">
-        <v>3</v>
-      </c>
-      <c r="P72" s="17" t="n">
-        <v>49.2</v>
+        <v>4</v>
+      </c>
+      <c r="P72" s="7" t="n">
+        <v>18.6</v>
       </c>
       <c r="Q72" s="8" t="n">
-        <v>3.732</v>
+        <v>6.658</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>6514</v>
@@ -62781,8 +62781,8 @@
       <c r="A73" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="n">
-        <v>35</v>
+      <c r="B73" s="14" t="n">
+        <v>50</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -62796,17 +62796,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6473.T</t>
+          <t>9007.T</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ジェイテクト</t>
+          <t>小田急電鉄</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>資本財</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -62815,31 +62815,31 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>1750</v>
+        <v>1631.5</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>1967.52</v>
+        <v>1720.3</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-11.056</v>
+        <v>-5.162</v>
       </c>
       <c r="L73" s="20" t="n">
         <v>2.2</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>2.86</v>
+        <v>2.45</v>
       </c>
       <c r="N73" s="5" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="O73" t="n">
-        <v>4</v>
-      </c>
-      <c r="P73" s="7" t="n">
-        <v>18.6</v>
+        <v>3</v>
+      </c>
+      <c r="P73" s="17" t="n">
+        <v>49.2</v>
       </c>
       <c r="Q73" s="8" t="n">
-        <v>6.658</v>
+        <v>3.732</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>6514</v>
@@ -63664,7 +63664,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -63678,17 +63678,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>8267.T</t>
+          <t>1332.T</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>イオン</t>
+          <t>日本水産</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>一般消費財</t>
+          <t>生活必需品</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -63697,31 +63697,31 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>2019</v>
+        <v>1354</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>2185.33</v>
+        <v>1467.9</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-7.611</v>
+        <v>-7.759</v>
       </c>
       <c r="L86" s="20" t="n">
         <v>2.85</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0.66</v>
+        <v>2.07</v>
       </c>
       <c r="N86" s="5" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="O86" t="n">
-        <v>2</v>
+        <v>2.13</v>
+      </c>
+      <c r="O86" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="P86" s="7" t="n">
-        <v>29.6</v>
+        <v>13.2</v>
       </c>
       <c r="Q86" s="8" t="n">
-        <v>5.332</v>
+        <v>5.433</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>6514</v>
@@ -63732,7 +63732,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -63746,17 +63746,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>1332.T</t>
+          <t>8267.T</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>日本水産</t>
+          <t>イオン</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>生活必需品</t>
+          <t>一般消費財</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -63765,31 +63765,31 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>1354</v>
+        <v>2019</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>1467.9</v>
+        <v>2185.33</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-7.759</v>
+        <v>-7.611</v>
       </c>
       <c r="L87" s="20" t="n">
         <v>2.85</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>2.07</v>
+        <v>0.66</v>
       </c>
       <c r="N87" s="5" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="O87" s="2" t="n">
-        <v>6</v>
+        <v>0.68</v>
+      </c>
+      <c r="O87" t="n">
+        <v>2</v>
       </c>
       <c r="P87" s="7" t="n">
-        <v>13.2</v>
+        <v>29.6</v>
       </c>
       <c r="Q87" s="8" t="n">
-        <v>5.433</v>
+        <v>5.332</v>
       </c>
       <c r="R87" s="9" t="n">
         <v>6514</v>
